--- a/data/cleaned/epl-dataset-clean.xlsx
+++ b/data/cleaned/epl-dataset-clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a411c4804a270cb/Desktop/prem-predictor/data/cleaned/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{EFD68E91-9BCB-407C-A560-F23F1D05F071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F085A679-54B5-486D-892D-5BD6A3E9DCE8}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="8_{EFD68E91-9BCB-407C-A560-F23F1D05F071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D16E053-AB57-4EC6-B210-246E2D907335}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{CACD530A-4E7C-4CD5-A416-101AE423E367}"/>
   </bookViews>
@@ -19915,10 +19915,12 @@
       <c r="H482" s="1">
         <v>86</v>
       </c>
-      <c r="I482" s="1"/>
+      <c r="I482" s="1">
+        <v>41</v>
+      </c>
       <c r="J482" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="K482" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -19953,10 +19955,12 @@
       <c r="H483" s="1">
         <v>69</v>
       </c>
-      <c r="I483" s="1"/>
+      <c r="I483" s="1">
+        <v>34</v>
+      </c>
       <c r="J483" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="K483" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -19991,10 +19995,12 @@
       <c r="H484" s="1">
         <v>72</v>
       </c>
-      <c r="I484" s="1"/>
+      <c r="I484" s="1">
+        <v>44</v>
+      </c>
       <c r="J484" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="K484" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20029,10 +20035,12 @@
       <c r="H485" s="1">
         <v>64</v>
       </c>
-      <c r="I485" s="1"/>
+      <c r="I485" s="1">
+        <v>43</v>
+      </c>
       <c r="J485" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="K485" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20067,10 +20075,12 @@
       <c r="H486" s="1">
         <v>68</v>
       </c>
-      <c r="I486" s="1"/>
+      <c r="I486" s="1">
+        <v>47</v>
+      </c>
       <c r="J486" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="K486" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20105,10 +20115,12 @@
       <c r="H487" s="1">
         <v>58</v>
       </c>
-      <c r="I487" s="1"/>
+      <c r="I487" s="1">
+        <v>51</v>
+      </c>
       <c r="J487" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="K487" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20143,10 +20155,12 @@
       <c r="H488" s="1">
         <v>58</v>
       </c>
-      <c r="I488" s="1"/>
+      <c r="I488" s="1">
+        <v>46</v>
+      </c>
       <c r="J488" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="K488" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20181,10 +20195,12 @@
       <c r="H489" s="1">
         <v>66</v>
       </c>
-      <c r="I489" s="1"/>
+      <c r="I489" s="1">
+        <v>59</v>
+      </c>
       <c r="J489" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="K489" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20219,10 +20235,12 @@
       <c r="H490" s="1">
         <v>58</v>
       </c>
-      <c r="I490" s="1"/>
+      <c r="I490" s="1">
+        <v>46</v>
+      </c>
       <c r="J490" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="K490" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20257,10 +20275,12 @@
       <c r="H491" s="1">
         <v>66</v>
       </c>
-      <c r="I491" s="1"/>
+      <c r="I491" s="1">
+        <v>57</v>
+      </c>
       <c r="J491" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="K491" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20295,10 +20315,12 @@
       <c r="H492" s="1">
         <v>54</v>
       </c>
-      <c r="I492" s="1"/>
+      <c r="I492" s="1">
+        <v>54</v>
+      </c>
       <c r="J492" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K492" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20333,10 +20355,12 @@
       <c r="H493" s="1">
         <v>51</v>
       </c>
-      <c r="I493" s="1"/>
+      <c r="I493" s="1">
+        <v>51</v>
+      </c>
       <c r="J493" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K493" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20371,10 +20395,12 @@
       <c r="H494" s="1">
         <v>42</v>
       </c>
-      <c r="I494" s="1"/>
+      <c r="I494" s="1">
+        <v>44</v>
+      </c>
       <c r="J494" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>42</v>
+        <v>-2</v>
       </c>
       <c r="K494" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20409,10 +20435,12 @@
       <c r="H495" s="1">
         <v>46</v>
       </c>
-      <c r="I495" s="1"/>
+      <c r="I495" s="1">
+        <v>62</v>
+      </c>
       <c r="J495" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>46</v>
+        <v>-16</v>
       </c>
       <c r="K495" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20447,10 +20475,12 @@
       <c r="H496" s="1">
         <v>44</v>
       </c>
-      <c r="I496" s="1"/>
+      <c r="I496" s="1">
+        <v>54</v>
+      </c>
       <c r="J496" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>44</v>
+        <v>-10</v>
       </c>
       <c r="K496" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20485,10 +20515,12 @@
       <c r="H497" s="1">
         <v>54</v>
       </c>
-      <c r="I497" s="1"/>
+      <c r="I497" s="1">
+        <v>69</v>
+      </c>
       <c r="J497" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>54</v>
+        <v>-15</v>
       </c>
       <c r="K497" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20523,10 +20555,12 @@
       <c r="H498" s="1">
         <v>64</v>
       </c>
-      <c r="I498" s="1"/>
+      <c r="I498" s="1">
+        <v>65</v>
+      </c>
       <c r="J498" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>64</v>
+        <v>-1</v>
       </c>
       <c r="K498" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20561,10 +20595,12 @@
       <c r="H499" s="1">
         <v>33</v>
       </c>
-      <c r="I499" s="1"/>
+      <c r="I499" s="1">
+        <v>80</v>
+      </c>
       <c r="J499" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>33</v>
+        <v>-47</v>
       </c>
       <c r="K499" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20599,10 +20635,12 @@
       <c r="H500" s="1">
         <v>36</v>
       </c>
-      <c r="I500" s="1"/>
+      <c r="I500" s="1">
+        <v>82</v>
+      </c>
       <c r="J500" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>36</v>
+        <v>-46</v>
       </c>
       <c r="K500" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
@@ -20637,10 +20675,12 @@
       <c r="H501" s="1">
         <v>26</v>
       </c>
-      <c r="I501" s="1"/>
+      <c r="I501" s="1">
+        <v>86</v>
+      </c>
       <c r="J501" s="1">
         <f>Table1[[#This Row],[GF]]-Table1[[#This Row],[GA]]</f>
-        <v>26</v>
+        <v>-60</v>
       </c>
       <c r="K501" s="1">
         <f>(Table1[[#This Row],[W]]*3)+Table1[[#This Row],[D]]</f>
